--- a/artfynd/A 42734-2025 artfynd.xlsx
+++ b/artfynd/A 42734-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128339727</v>
+        <v>128339726</v>
       </c>
       <c r="B2" t="n">
-        <v>97356</v>
+        <v>78790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>794072</v>
+        <v>793863</v>
       </c>
       <c r="R2" t="n">
-        <v>7416951</v>
+        <v>7417000</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339726</v>
+        <v>128339727</v>
       </c>
       <c r="B3" t="n">
-        <v>78789</v>
+        <v>97361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>793863</v>
+        <v>794072</v>
       </c>
       <c r="R3" t="n">
-        <v>7417000</v>
+        <v>7416951</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>128339724</v>
       </c>
       <c r="B4" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340213</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340215</v>
       </c>
       <c r="B6" t="n">
-        <v>91530</v>
+        <v>91535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128339722</v>
       </c>
       <c r="B7" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128339728</v>
       </c>
       <c r="B8" t="n">
-        <v>98390</v>
+        <v>98395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128339723</v>
       </c>
       <c r="B9" t="n">
-        <v>80163</v>
+        <v>80164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42734-2025 artfynd.xlsx
+++ b/artfynd/A 42734-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339726</v>
       </c>
       <c r="B2" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339727</v>
       </c>
       <c r="B3" t="n">
-        <v>97361</v>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339724</v>
       </c>
       <c r="B4" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340213</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340215</v>
       </c>
       <c r="B6" t="n">
-        <v>91535</v>
+        <v>91627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128339722</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128339728</v>
       </c>
       <c r="B8" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128339723</v>
       </c>
       <c r="B9" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42734-2025 artfynd.xlsx
+++ b/artfynd/A 42734-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128339726</v>
+        <v>128339727</v>
       </c>
       <c r="B2" t="n">
-        <v>78840</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>793863</v>
+        <v>794072</v>
       </c>
       <c r="R2" t="n">
-        <v>7417000</v>
+        <v>7416951</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339727</v>
+        <v>128339726</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>794072</v>
+        <v>793863</v>
       </c>
       <c r="R3" t="n">
-        <v>7416951</v>
+        <v>7417000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>128339724</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340213</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340215</v>
       </c>
       <c r="B6" t="n">
-        <v>91627</v>
+        <v>91639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128339722</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128339728</v>
       </c>
       <c r="B8" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128339723</v>
       </c>
       <c r="B9" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42734-2025 artfynd.xlsx
+++ b/artfynd/A 42734-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128339727</v>
+        <v>128339726</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>794072</v>
+        <v>793863</v>
       </c>
       <c r="R2" t="n">
-        <v>7416951</v>
+        <v>7417000</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339726</v>
+        <v>128339727</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>97468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>793863</v>
+        <v>794072</v>
       </c>
       <c r="R3" t="n">
-        <v>7417000</v>
+        <v>7416951</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>128339724</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340213</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340215</v>
       </c>
       <c r="B6" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128339722</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128339728</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128339723</v>
       </c>
       <c r="B9" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42734-2025 artfynd.xlsx
+++ b/artfynd/A 42734-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128340213</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128339728</v>
       </c>
       <c r="B8" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42734-2025 artfynd.xlsx
+++ b/artfynd/A 42734-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128339726</v>
+        <v>128339727</v>
       </c>
       <c r="B2" t="n">
-        <v>78846</v>
+        <v>97469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>793863</v>
+        <v>794072</v>
       </c>
       <c r="R2" t="n">
-        <v>7417000</v>
+        <v>7416951</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339727</v>
+        <v>128339726</v>
       </c>
       <c r="B3" t="n">
-        <v>97468</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>794072</v>
+        <v>793863</v>
       </c>
       <c r="R3" t="n">
-        <v>7416951</v>
+        <v>7417000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>128340213</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340215</v>
       </c>
       <c r="B6" t="n">
-        <v>91641</v>
+        <v>91642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128339728</v>
       </c>
       <c r="B8" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42734-2025 artfynd.xlsx
+++ b/artfynd/A 42734-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128339727</v>
+        <v>128339726</v>
       </c>
       <c r="B2" t="n">
-        <v>97469</v>
+        <v>78873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>794072</v>
+        <v>793863</v>
       </c>
       <c r="R2" t="n">
-        <v>7416951</v>
+        <v>7417000</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339726</v>
+        <v>128339727</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>793863</v>
+        <v>794072</v>
       </c>
       <c r="R3" t="n">
-        <v>7417000</v>
+        <v>7416951</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>128339724</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340213</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340215</v>
       </c>
       <c r="B6" t="n">
-        <v>91642</v>
+        <v>91669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128339722</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128339728</v>
       </c>
       <c r="B8" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128339723</v>
       </c>
       <c r="B9" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42734-2025 artfynd.xlsx
+++ b/artfynd/A 42734-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339726</v>
       </c>
       <c r="B2" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339727</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339724</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340213</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340215</v>
       </c>
       <c r="B6" t="n">
-        <v>91669</v>
+        <v>91679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128339722</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128339728</v>
       </c>
       <c r="B8" t="n">
-        <v>98536</v>
+        <v>98549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128339723</v>
       </c>
       <c r="B9" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42734-2025 artfynd.xlsx
+++ b/artfynd/A 42734-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339726</v>
       </c>
       <c r="B2" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339727</v>
       </c>
       <c r="B3" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339724</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340213</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340215</v>
       </c>
       <c r="B6" t="n">
-        <v>91679</v>
+        <v>91683</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128339722</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128339728</v>
       </c>
       <c r="B8" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128339723</v>
       </c>
       <c r="B9" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
